--- a/tame_output/ON/bt/strategyON_20240115.xlsx
+++ b/tame_output/ON/bt/strategyON_20240115.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.1%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>101.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.0%</t>
+          <t>130.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1842"/>
+  <dimension ref="A1:G1843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293724427206153</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43927,6 +43927,29 @@
       </c>
       <c r="G1842" t="n">
         <v>4.480972528538612</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="2" t="n">
+        <v>45305</v>
+      </c>
+      <c r="B1843" t="n">
+        <v>3.293329894960367</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>3.126480719537785</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>1.62819783620631</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>3.777403429706562</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>2.241866401647637</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>4.471600560526368</v>
       </c>
     </row>
   </sheetData>
